--- a/Result/profitability/3557.xlsx
+++ b/Result/profitability/3557.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0.39</v>
+        <v>0.27875</v>
       </c>
       <c r="N2" t="n">
-        <v>32.455</v>
+        <v>32.76125</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.27</v>
+        <v>0.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>30.23375</v>
+        <v>30.41125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.19</v>
+        <v>-0.1175</v>
       </c>
       <c r="N4" t="n">
-        <v>28.735</v>
+        <v>28.875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1675</v>
+        <v>0.02500000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>23.4025</v>
+        <v>23.975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01000000000000003</v>
+        <v>0.215</v>
       </c>
       <c r="N6" t="n">
-        <v>21.2275</v>
+        <v>22.12</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.275</v>
+        <v>0.26375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.755</v>
+        <v>21.3575</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2812500000000001</v>
+        <v>0.245</v>
       </c>
       <c r="N8" t="n">
-        <v>19.45875</v>
+        <v>19.8275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>-0.44</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08250000000000005</v>
+        <v>0.0825</v>
       </c>
       <c r="N12" t="n">
         <v>12.90375</v>
@@ -2026,7 +2026,7 @@
         <v>-0.96</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01124999999999995</v>
+        <v>-0.01124999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>12.205</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>964</v>
+      </c>
+      <c r="D75" t="n">
+        <v>605</v>
+      </c>
+      <c r="E75" t="n">
+        <v>359</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>48</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>25</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6041666666666666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.950000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0859306728808622</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.140740740740741</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.579999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1400611620795107</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
